--- a/Data/GP2_ADFI_summary.xlsx
+++ b/Data/GP2_ADFI_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3369B0ED-7802-4FCD-AFBF-98DFD35D11E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D767F01-FD3D-4EF6-9BA9-AAB222751981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -412,9 +412,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -460,7 +463,7 @@
         <v>1.1108216088921701</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -483,7 +486,7 @@
         <v>1.083427319515204</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -506,7 +509,7 @@
         <v>0.82777529011575157</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -529,7 +532,7 @@
         <v>0.99163890792206533</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -552,7 +555,7 @@
         <v>1.506391406854023</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -575,7 +578,7 @@
         <v>1.23974007568483</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -598,7 +601,7 @@
         <v>0.9411285816250502</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -621,7 +624,7 @@
         <v>1.141645419901834</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -644,7 +647,7 @@
         <v>1.9350810411885091</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -667,7 +670,7 @@
         <v>0.59999999999999964</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -690,7 +693,7 @@
         <v>0.87798828140926444</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -713,7 +716,7 @@
         <v>0.75051003066078281</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -736,7 +739,7 @@
         <v>0.68728071998934603</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -759,7 +762,7 @@
         <v>0.65825276550630862</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -782,7 +785,7 @@
         <v>0.45702264903048789</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -805,7 +808,7 @@
         <v>0.98172468620160769</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -828,7 +831,7 @@
         <v>0.72618657297936196</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -851,7 +854,7 @@
         <v>0.66752430443937283</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -874,7 +877,7 @@
         <v>0.64039822775355193</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -897,7 +900,7 @@
         <v>0.80000000000000071</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -920,7 +923,7 @@
         <v>0.81943618860162193</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -943,7 +946,7 @@
         <v>1.103327349515266</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -966,7 +969,7 @@
         <v>0.74055605672725155</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -989,7 +992,7 @@
         <v>1.4659451867051041</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1012,7 +1015,7 @@
         <v>1.2597391397257549</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>0.85025621773250137</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1058,7 +1061,7 @@
         <v>0.9167463454262762</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1081,7 +1084,7 @@
         <v>1.075523310981533</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1104,7 +1107,7 @@
         <v>0.60201128097202827</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1130,7 @@
         <v>0.86480095440386384</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>0.48848595100863451</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1173,7 +1176,7 @@
         <v>1.0336869130558439</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>0.15365765532262449</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>0.18952141659173721</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -1242,7 +1245,7 @@
         <v>0.33724807447376731</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1265,7 +1268,7 @@
         <v>0.64717718173046734</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>0.93019300507346236</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>6.0867615051104378E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>0.77981803617558187</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -1357,7 +1360,7 @@
         <v>1.073286392962606</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>1.6295892809201331</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -1403,7 +1406,7 @@
         <v>0.99183281811476776</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -1426,7 +1429,7 @@
         <v>0.67841235845204872</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -1449,7 +1452,7 @@
         <v>0.88492964181205613</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>0.96423331155943748</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>1.289631167381081</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -1518,7 +1521,7 @@
         <v>1.429923810421617</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>2.2749999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -1564,7 +1567,7 @@
         <v>0.89035473501303153</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>0.54252447875381238</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -1610,7 +1613,7 @@
         <v>0.87394700039398576</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -1633,7 +1636,7 @@
         <v>0.72580816213794386</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -1656,7 +1659,7 @@
         <v>0.45288192811849598</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -1679,7 +1682,7 @@
         <v>0.48456554526803752</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>0.63687078407193043</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -1725,7 +1728,7 @@
         <v>0.67899639671385037</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>0.31039044637258417</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -1771,7 +1774,7 @@
         <v>0.602089506585479</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>0.46620482491659199</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -1817,7 +1820,7 @@
         <v>0.94223256035980718</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -1840,7 +1843,7 @@
         <v>0.89512897784072032</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -1863,7 +1866,7 @@
         <v>0.43374170670096751</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -1886,7 +1889,7 @@
         <v>0.88284718512112581</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -1909,7 +1912,7 @@
         <v>1.0512369368183561</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>0.93606653884707181</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>0.80426160836749971</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>1.849999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -2001,7 +2004,7 @@
         <v>0.94874121345596141</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -2024,7 +2027,7 @@
         <v>0.65633012331389362</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2047,7 +2050,7 @@
         <v>0.98085279909922507</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -2070,7 +2073,7 @@
         <v>0.36505520969087529</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>0.13194594773625609</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -2116,7 +2119,7 @@
         <v>0.26863805579915118</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -2139,7 +2142,7 @@
         <v>0.71089304174220769</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -2162,7 +2165,7 @@
         <v>0.519766280044475</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -2185,7 +2188,7 @@
         <v>0.1714285714285714</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>12</v>
       </c>
